--- a/new-stats/talaea-el-gaish-sc.xlsx
+++ b/new-stats/talaea-el-gaish-sc.xlsx
@@ -511,22 +511,62 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>El Gaish</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Arab Contractors</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>

--- a/new-stats/talaea-el-gaish-sc.xlsx
+++ b/new-stats/talaea-el-gaish-sc.xlsx
@@ -569,58 +569,178 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Petrojet</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>El Gaish</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>16</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>El Gaish</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ZED</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Al Qanah</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>El Gaish</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>

--- a/new-stats/talaea-el-gaish-sc.xlsx
+++ b/new-stats/talaea-el-gaish-sc.xlsx
@@ -743,22 +743,62 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>El Gaish</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Smouha</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>

--- a/new-stats/talaea-el-gaish-sc.xlsx
+++ b/new-stats/talaea-el-gaish-sc.xlsx
@@ -801,22 +801,62 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>National Bank Egypt</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>El Gaish</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M7" t="n">
+        <v>21</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>

--- a/new-stats/talaea-el-gaish-sc.xlsx
+++ b/new-stats/talaea-el-gaish-sc.xlsx
@@ -859,22 +859,62 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>El Gaish</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pyramids</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M8" t="n">
+        <v>16</v>
+      </c>
+      <c r="N8" t="n">
+        <v>22</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
